--- a/Result/checksun_type/基板組裝加工及相關製造.xlsx
+++ b/Result/checksun_type/基板組裝加工及相關製造.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.7</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>33.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13200.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>15096.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>15096.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>19230.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25701.88</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25701.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-4973.313594370433</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13200</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13200.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>32.59</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>31.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>28811.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14684.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>14684.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>19867.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>25691.78</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>25691.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-4992.378641688298</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>28811</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>28811.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>32.53</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>33.51</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>31.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6859.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>12190.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>12190.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>19124.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>25282.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>25282.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-6513.922329224952</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6859</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6859.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>32.83</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>33.44</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>31.2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>11471.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>15493.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>15493.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>20323.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>25414.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>25414.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-6102.916085376422</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>11471</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>11471.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>33.38</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>31.16</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>31.16</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>15141.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>18318.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>18318.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>20954.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>25419.46</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>25419.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-5791.94587682937</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>15141</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>15141.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>33.71</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.22</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>11142.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>23365.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>23365.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>26533.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>25381.56</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>25381.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-5534.061797589675</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>11142</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>11142.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.14</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31.05</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>16340.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>25050.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>25050.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>28685.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>25676.3</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>25676.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-4539.546620190478</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>16340</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>16340.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>34.33</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.01</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>23372.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>26058.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>26058.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>35334.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>25960.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>25960.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-3513.612558899105</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>23372</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>23372.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>34.25</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>25598.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>25153.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>25153.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>62839.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>26429.32</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>26429.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2675.93487995075</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>25598</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>25598.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>34.14</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>30.89</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>30.89</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>40374.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>23590.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>23590.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>73968.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>28339.88</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>28339.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1622.183378597714</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>40374</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>40374.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>34.03</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>32.24</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>30.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>19569.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>29701.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>29701.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>72921.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>31652.32</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>31652.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1642.031827429171</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>19569</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>19569.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>86.05999999999999</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>88.59</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>93.22</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>93.22</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>39222746.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>37069649.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>37069649</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>52143488.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>115780162.98</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>115780162.98</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-7767080.813954495</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>39222746</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>39222746.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>85.5</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>88.72</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>93.68</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>88.72</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>93.68000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>32232668.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>40262190.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>40262190.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>58190353.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>129955842.22</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>129955842.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-8102783.78151498</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>32232668</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>32232668.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>85.44000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>88.92</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>94.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>94.23999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>29001475.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>51177173.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>51177173</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>59037855.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>144246848.4</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>144246848.4</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-7544037.385832988</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>29001475</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>29001475.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>86.48</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>89.21</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>94.9</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>89.20999999999999</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>50679890.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>57169558.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>57169558.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>60803272.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>168657861.26</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>168657861.26</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-6130199.092507534</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>50679890</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>50679890.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>87.56</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>89.52</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>95.56</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>95.56</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>34211466.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>61308928.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>61308928.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>60197278.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>190216917.98</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>190216917.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-6214181.741595916</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>34211466</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34211466.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>88.52000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>89.66</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>96.15</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>96.15000000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>55185452.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>67217327.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>67217327.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>60001860.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>237899946.18</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>237899946.18</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-4347747.892379463</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>55185452</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>55185452.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>90.16</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>96.67</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>96.67</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>86807582.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>76118517.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>76118517</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>58913884.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>266511314.06</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>266511314.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-3773349.897342399</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>86807582</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>86807582.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>90.94000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>97.19</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>97.19</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>58963401.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>66898538.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>66898538.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>59790098.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>295009065.8</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>295009065.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-6206104.193812944</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>58963401</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>58963401.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>90.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>89.84</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>97.5</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>71376741.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>64436986.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>64436986</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>70324553.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>306337018.38</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>306337018.38</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-6476515.788991831</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>71376741</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>71376741.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>90.52000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>89.92</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>97.87</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>97.87</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>63753463.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>59085628.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>59085628</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>67432418.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>334235246.34</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>334235246.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-7961514.646783389</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>63753463</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>63753463.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>89.91999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>89.72</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>98.21</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>98.20999999999999</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>99691398.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>52786392.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>52786392.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>65682247.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>375653033.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>375653033</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-8981821.991957627</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>99691398</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>99691398.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>50.51000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>60.65</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>60.65</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>65653830.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>66218180.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>66218180.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>80200182.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>136018349.8</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>136018349.8</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-14717074.9081188</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>65653830</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>65653830.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>49.76000000000001</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>55.81</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>60.89</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>60.89</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>54935297.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>74643551.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>74643551.40000001</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>84659426.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>139858021.14</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>139858021.14</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-14998236.7171105</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>54935297</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>54935297.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>49.7</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>61.15</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>61.15</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>62003903.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>79053173.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>79053173.40000001</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>93140284.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>141144956.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>141144956.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-13715830.88291614</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>62003903</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>62003903.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>50.01000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>57.34</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>61.42</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>61.42</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>59794555.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>88533850.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>88533850.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>117373464.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>142724160.18</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>142724160.18</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-12151322.0882486</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>59794555</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>59794555.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>50.73</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>58.18</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>61.73</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>61.73</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>88703317.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>93174113.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>93174113.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>163193145.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>143157140.72</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>143157140.72</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-9245617.87842895</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>88703317</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>88703317.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>51.47000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>58.94</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>62.03</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>62.03</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>107780685.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>94182185.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>94182185</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>160055065.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>143086948.4</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>143086948.4</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-7861778.583028436</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>107780685</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>107780685.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>52.18000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>59.73</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>62.35</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>62.35</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>76983407.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>94675302.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>94675302</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>157875819.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>143947609.18</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>143947609.18</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-7648091.211633801</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>76983407</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>76983407.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>62.62</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>62.62</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>109407290.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>107227395.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>107227395.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>156134004.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>143994874.78</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>143994874.78</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3769969.066368848</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>109407290</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>109407290.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>53.06</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>60.84</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>62.88</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>62.88</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>82995867.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>146213078.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>146213078.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>155458226.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>144752624.76</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>144752624.76</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1569140.285048604</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>82995867</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>82995867.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>53.82000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>61.34</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>63.15</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>63.15</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>93743676.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>233212177.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>233212177</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>154974655.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>147399928.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>147399928.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>4460736.877017766</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>93743676</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>93743676.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>55.67999999999999</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>61.75</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>63.44</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>63.44</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>110246270.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>225927945.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>225927945.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>153357947.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>148472944.36</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>148472944.36</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>11763984.11293343</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>110246270</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>110246270.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>28.34</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>29.28</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>29.77</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>29.77</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2761.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>6211.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>6211.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>6500.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>5806.58</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>5806.58</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-281.9420058826572</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2761</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2761.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>28.4</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>29.81</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>29.81</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>5314.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>7040.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>7040.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>6637.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>5879.68</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>5879.68</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>18.89924342806989</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>5314</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>5314.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>28.61</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>29.86</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>29.86</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>6462.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>7358.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>7358.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>6596.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>5856.88</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>5856.88</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>174.46176946382</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>6462</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>6462.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>28.95</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>29.92</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>8638.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>7944.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>7944.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>6845.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>5812.2</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>5812.2</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>267.4631720340421</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>8638</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>8638.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>29.17</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>29.96</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>7883.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>7210.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>7210</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>6463.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>5721.94</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>5721.94</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>157.6272052759996</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>7883</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>7883.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>29.29</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>29.77</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>30</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>6905.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>6790.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>6790.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>5940.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>5722.24</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>5722.24</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>75.98199543322517</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>6905</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>6905.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>29.44</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>30.05</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6905.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>6235.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>6235</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>6109.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>5689.16</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>5689.16</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>61.41805296378971</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6905</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6905.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,21 +18257,17 @@
           <t>29.45</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>29.87</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AM42" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>30.09</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>30.09</t>
-        </is>
-      </c>
       <c r="AP42" t="inlineStr">
         <is>
           <t>-20.86</t>
@@ -18552,20 +18308,16 @@
           <t>9391.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>5834.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>5834.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>6009.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>5655.08</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>5655.08</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>38.4189189730314</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>9391</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>9391.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>29.36</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>29.88</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>30.12</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>30.12</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>4966.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>5747.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>5747</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>5443.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>5672.26</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>5672.26</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-262.1662338342303</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>4966</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>4966.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>29.43</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>30.16</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>30.16</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>5784.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>5717.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>5717</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>7021.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>5897.94</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>5897.94</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-208.1033723505234</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>5784</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>5784.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>29.5</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>29.93</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>30.2</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>30.2</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>4129.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>5090.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>5090.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>7174.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>5967.76</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>5967.76</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-211.0813069327105</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>4129</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>4129.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20055,11 +19791,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>6224</t>
@@ -20241,41 +19973,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr">
         <is>
           <t>0</t>
@@ -20296,20 +20024,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>0</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>117.0</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>117.02</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>116.87</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>116.87</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>9070170773.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>3776978493.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>3776978493.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>2831154552.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>2520902011.04</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>2520902011.04</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>399266594.8129096</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>9070170773</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>9070170773.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>112.3</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>116.25</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>116.93</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>116.93</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>3882697982.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>2257647782.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>2257647782.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>2137756702.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>2428147132.88</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>2428147132.88</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>-104554806.7083888</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>3882697982</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>3882697982.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>109.1</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>115.58</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>117.24</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>115.58</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>117.24</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>1134395701.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1939994443.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1939994443.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>2011648397.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>2464569804.24</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>2464569804.24</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>-264764909.6063719</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1134395701</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1134395701.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>109.7</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>115.4</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>117.69</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>117.69</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>2737544262.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>2017338280.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>2017338280.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>2307584325.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>2538700353.3</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>2538700353.3</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>-189719636.8675485</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2737544262</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2737544262.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>110.7</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>115.2</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>118.16</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>118.16</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>2060083751.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1859193365.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1859193365.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>2482215593.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>2560004084.98</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>2560004084.98</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>-247502320.3168173</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>2060083751</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>2060083751.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>112.4</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>114.8</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>118.58</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>118.58</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>1473517218.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1885330610.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1885330610.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>2998421834.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>2651313183.92</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>2651313183.92</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>-248624587.6258864</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1473517218</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1473517218.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>115.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>115.08</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>119.23</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>115.08</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>119.23</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>2294431285.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>2017865623.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>2017865623</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>3222458623.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2810393782.38</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2810393782.38</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>-178501962.8307748</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>2294431285</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>2294431285.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>117.3</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>115.05</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>120.04</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>120.04</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>1521114885.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>2083302352.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>2083302352.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>3980871833.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2983118353.94</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2983118353.94</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>-159906793.0580878</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1521114885</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1521114885.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>118.2</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>114.7</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>120.46</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>120.46</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>1946819688.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2597830371.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2597830371.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4244155474.6</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>3129392785.5</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>3129392785.5</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>-44775979.34503222</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1946819688</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1946819688.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>120.1</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>120.77</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>120.77</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>2190769978.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3105237822.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3105237822.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>4642637970.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>3288771508.7</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>3288771508.7</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>75684524.90022707</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>2190769978</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>2190769978.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>121.4</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>113.75</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>121.2</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>121.2</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>2136192279.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>4111513058.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>4111513058.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>4642599460.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>3494069773.8</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>3494069773.8</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>218930409.7184467</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2136192279</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2136192279.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>26.47</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>22.44</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>2302106.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1011071.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1011071.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>885382.1</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>421472.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>421472.2</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>161057.9456006828</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2302106</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2302106.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>26.4</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>22.29</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>22.29</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>1289098.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>686188.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>686188.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>736720.7</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>378101.64</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>378101.64</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>49551.95832136797</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1289098</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1289098.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>26.12</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>25.42</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>22.12</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>22.12</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>439916.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>614902.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>614902.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>642506.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>355793.56</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>355793.56</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>-2975.450589130516</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>439916</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>439916.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>26.3</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>25.33</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>22.02</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>373578.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>704190.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>704190.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>630098.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>351805.88</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>351805.88</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>13075.44563119789</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>373578</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>373578.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>26.64</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>21.92</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>650659.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>689166.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>689166.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>646505.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>345830.74</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>345830.74</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>42645.96003055281</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>650659</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>650659.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>26.66</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>21.77</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>21.77</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>677690.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>759692.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>759692.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>698822.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>335168.96</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>335168.96</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>53679.23202853999</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>677690</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>677690.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>26.59</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>21.63</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>21.63</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>932668.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>787253.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>787253.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>751295.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>327045.38</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>327045.38</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>64627.75516750244</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>932668</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>932668.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>24.34</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>21.5</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>21.5</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>886358.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>670111.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>670111.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>689218.2</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>311593.08</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>311593.08</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>50641.29696718091</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>886358</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>886358.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>25.56</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>21.4</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>298457.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>556006.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>556006</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>643379.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>297986.56</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>297986.56</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>33813.81036075065</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>298457</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>298457.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>25.47</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>23.59</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>21.34</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>21.34</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>1003291.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>603843.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>603843.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>652085.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>295859.72</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>295859.72</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>71556.30055296642</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1003291</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1003291.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>25.23</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>23.21</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>21.3</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>815492.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>637952.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>637952.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>592480.9</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>280149.9</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>280149.9</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>47400.63295066881</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>815492</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>815492.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>23.81</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>23.87</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>23.18</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>23.18</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>39444.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>62992.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>62992.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>45486.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>43879.04</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>43879.04</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-3975.805367332854</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>39444</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>39444.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>23.44</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>23.17</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>23.17</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>62964.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>57517.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>57517.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>48308.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>43826.16</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>43826.16</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-3029.643795471588</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>62964</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>62964.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>23.04</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>23.18</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>23.18</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>73834.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>47460.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>47460.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>44962.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>43147.02</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>43147.02</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-4089.782842974368</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>73834</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>73834.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>22.96</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>23.2</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>40160.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>35455.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>35455.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>41249.2</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>42160.92</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>42160.92</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-6622.846380729257</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>40160</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>40160.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>23.04</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>23.48</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>98561.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>31684.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>31684.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>40115.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>41699.24</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>41699.24</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-6397.049778210188</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>98561</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>98561.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>23.1</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>23.27</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>12070.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>27980.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>27980.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>37110.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>40198.12</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>40198.12</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-12103.26713967544</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>12070</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>12070.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>23.67</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>23.33</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>12677.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>39099.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>39099.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>43688.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>40734.76</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>40734.76</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-10555.8538296374</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>12677</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>12677.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>23.7</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>23.35</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>13808.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>42463.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>42463.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>91728.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>40962.7</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>40962.7</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-8033.3043213817</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>13808</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>13808.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>23.66</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>23.43</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>23.43</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>21306.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>47043.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>47043.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>129167.9</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>41172.92</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>41172.92</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-4263.937012395647</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>21306</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>21306.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>23.8</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>23.47</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>80040.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>48545.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>48545.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>135852.4</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>41482.14</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>41482.14</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>469.7997508842818</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>80040</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>80040.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>23.97</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>23.51</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>67665.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>46240.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>46240.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>130923.8</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>40698.64</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>40698.64</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>922.5737073240161</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>67665</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>67665.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>5.923999999999999</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>8.03</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>7.82</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>7.82</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>784.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>3116.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>3116.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>5274.8</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>5723.26</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>5723.26</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>-1214.053521820129</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>784</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>784.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>6.093999999999999</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>8.19</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>7.87</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>7.87</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>1324.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>4285.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>4285.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>5944.9</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>5809.18</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>5809.18</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>-990.3546049857432</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1324</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1324.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>6.426</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>8.31</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>7.93</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>7.93</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>3409.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>7854.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>7854</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>6700.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>5886.96</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>5886.96</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>-693.2720593299864</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>3409</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>3409.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>6.894</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>7.99</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>3881.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>7778.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>7778</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>7023.8</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>5928.08</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>5928.08</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>-467.5015634171195</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>3881</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>3881.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>7.470000000000001</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>8.47</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>8.05</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>8.050000000000001</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>6183.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>7819.8</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>7819.8</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>7094.1</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>5926.92</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>5926.92</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>-178.8472277052706</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>6183</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>6183.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>7.956</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>8.109999999999999</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>6632.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>7433.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>7433.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>6988.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>5885.42</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>5885.42</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>-6.739347127440851</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>6632</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>6632.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>8.338</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>8.51</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>8.15</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>19165.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>7604.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>7604</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>6877.0</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>5796.08</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>5796.08</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>191.2626018097253</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>19165</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>19165.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>8.565999999999999</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>8.46</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>8.19</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>8.19</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>3029.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>5546.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>5546.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>6652.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>5448.86</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>5448.86</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>-875.5297069161006</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>3029</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>3029.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>8.791999999999998</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>8.39</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>8.21</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>8.210000000000001</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>4090.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>6269.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>6269.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>9330.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>5412.44</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>5412.44</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>-639.3926584202763</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>4090</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>4090.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>8.953999999999999</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>8.32</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>8.23</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>8.23</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>4251.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>6368.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>6368.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>9798.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>5375.12</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>5375.12</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-392.8971370540885</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>4251</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>4251.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>9.08</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>8.24</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>8.25</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>7485.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>6543.6</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>6543.6</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>13261.3</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>5395.02</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>5395.02</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-43.97863735045939</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>7485</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>7485.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>1578.0</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>1508.25</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>1297.34</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>1508.25</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>1297.34</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>8660559640.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>12655765945.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>12655765945.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>9186859988.8</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>4926093528.12</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>4926093528.12</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>1587065451.454584</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>8660559640</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>8660559640.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>1594.0</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>1506.25</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>1289.84</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>1506.25</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1289.84</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>14268998085.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>11903064950.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>11903064950.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>8830581319.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>4817341249.12</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>4817341249.12</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>2015843897.12149</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>14268998085</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>14268998085.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>1599.0</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>1501.25</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>1281.64</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>1501.25</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1281.64</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>28742044615.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>10298542898.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>10298542898.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>8042654289.3</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>4598697520.32</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>4598697520.32</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>1955485989.784161</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>28742044615</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>28742044615.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>1612.0</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>1491.75</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>1272.24</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1272.24</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>6169714440.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>5728226103.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>5728226103</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>5811772650.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>4091228347.42</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>4091228347.42</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>248738065.7385426</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>6169714440</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>6169714440.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>1478.0</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>1261.84</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>1478</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>1261.84</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>5437512946.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>5661854900.6</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>5661854900.6</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>5608775910.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>4014085333.32</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>4014085333.32</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>220107190.6469994</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>5437512946</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>5437512946.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>1580.0</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>1460.0</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>1249.74</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1249.74</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>4897054665.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>5717954032.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>5717954032.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>5414291186.7</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>4036813613.2</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>4036813613.2</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>249795129.4931173</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>4897054665</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>4897054665.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>1564.0</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>1445.5</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>1239.34</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>1239.34</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>6246387825.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>5758097688.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>5758097688.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>5400232874.2</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>4111558830.4</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>4111558830.4</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>341191460.4699583</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>6246387825</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>6246387825.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>1560.0</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>1431.5</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>1227.28</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1227.28</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>5890460639.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>5786765680.4</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>5786765680.4</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>5177128699.2</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>4046244405.4</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>4046244405.4</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>315000828.2772322</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>5890460639</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>5890460639.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>1542.0</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>1415.0</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>1213.96</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>1415</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1213.96</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>5837858428.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>5895319198.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>5895319198.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>5008164336.8</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>4019510992.36</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>4019510992.36</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>304470665.4920092</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>5837858428</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>5837858428.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>1521.0</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>1203.08</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>1203.08</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>5718008605.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>5555696920.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>5555696920</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>4684194498.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>4026606885.46</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>4026606885.46</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>284189574.6384048</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>5718008605</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>5718008605.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>1474.0</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>1379.0</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>1192.48</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>1379</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1192.48</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>5097772945.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>5110628341.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>5110628341</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>4542311051.0</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>4058950208.26</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>4058950208.26</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>257908012.5033131</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>5097772945</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>5097772945.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>17.41</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>17.96</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>17.19</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>17.19</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>2289.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>3829.2</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>3829.2</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>4577.5</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>9869.76</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>9869.76</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>-1599.758500528125</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>2289</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>2289.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>17.5</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>18.08</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>17.13</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>3016.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>4025.4</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>4025.4</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>5151.8</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>9881.16</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>9881.16</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>-1589.306239763167</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>3016</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>3016.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>17.56</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>18.17</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>3994.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>4178.8</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>4178.8</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>5649.2</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>9884.86</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>9884.860000000001</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>-1595.506358678826</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>3994</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>3994.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>17.81</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>4477.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>4430.4</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>4430.4</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>6128.5</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>9850.2</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>9850.200000000001</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>-1652.167015748384</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>4477</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>4477.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>17.93</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>16.98</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>5370.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>4635.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>4635.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>6994.0</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>9790.38</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>9790.379999999999</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>-1725.854846713881</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>5370</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>5370.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>18.16</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>18.34</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>16.93</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>3270.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>5325.8</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>5325.8</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>6795.5</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>9701.12</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>9701.120000000001</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>-1865.164074996238</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>3270</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>3270.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>16.88</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>16.88</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>3783.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>6278.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>6278.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>7017.1</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>9663.06</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>9663.059999999999</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>-1772.564255578311</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>3783</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>3783.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>18.43</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>16.82</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>5252.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>7119.6</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>7119.6</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>8071.2</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>9603.68</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>9603.68</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-1631.937218710618</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>5252</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>5252.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>18.45</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>16.76</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>5502.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>7826.6</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>7826.6</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>8473.2</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>9526.46</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>9526.459999999999</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>-1530.150836802821</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>5502</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>5502.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>18.55</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>16.71</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>16.71</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>8822.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>9352.6</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>9352.6</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>9785.8</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>9458.56</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>9458.559999999999</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>-1356.879189905867</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>8822</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>8822.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>18.33</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>16.65</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>8032.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>8265.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>8265.200000000001</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>10893.4</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>9390.82</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>9390.82</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>-1416.602580413579</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>8032</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>8032.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48599,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48783,11 @@
           <t>46.48999999999999</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>50.44</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>53.09</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>53.09</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48834,16 @@
           <t>117272236.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>149000240.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>149000240.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>234177131.2</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>747762214.72</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>747762214.72</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48860,10 @@
           <t>-103803341.0046888</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>117272236</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>117272236.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49029,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49213,11 @@
           <t>46.3</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>53.29</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>53.29</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49264,16 @@
           <t>113631797.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>172237835.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>172237835.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>244788622.4</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>810985603.24</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>810985603.24</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49290,10 @@
           <t>-108294619.1586549</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>113631797</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>113631797.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49459,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49643,11 @@
           <t>46.33</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>51.47</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>53.58</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>53.58</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49694,16 @@
           <t>119170270.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>213890174.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>213890174.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>256565453.0</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>896170788.4</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>896170788.4</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49720,10 @@
           <t>-110453018.8015116</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>119170270</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>119170270.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49889,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50073,11 @@
           <t>46.79000000000001</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>53.76</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>53.76</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50124,16 @@
           <t>199365519.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>255534900.6</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>255534900.6</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>288106969.0</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>913461427.7</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>913461427.7</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50150,10 @@
           <t>-110185104.0126815</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>199365519</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>199365519.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50319,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50503,11 @@
           <t>47.66</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>53.96</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>53.96</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50554,16 @@
           <t>195561380.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>290690620.0</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>290690620</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>297011196.2</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>931528814.22</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>931528814.22</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50580,10 @@
           <t>-114459534.4210427</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>195561380</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>195561380.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50749,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50933,11 @@
           <t>48.33</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>52.96</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>54.1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50984,16 @@
           <t>233460211.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>319354022.0</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>319354022</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>307427651.6</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>941847348.14</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>941847348.14</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51010,10 @@
           <t>-116070436.7393787</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>233460211</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>233460211.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51179,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51363,11 @@
           <t>49.45</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>53.47</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>54.27</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>54.27</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51414,16 @@
           <t>321893492.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>317339409.4</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>317339409.4</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>324620319.3</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>961377045.06</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>961377045.0599999</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51440,10 @@
           <t>-118286942.060595</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>321893492</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>321893492.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51793,11 @@
           <t>50.35</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>53.93</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>54.46</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>54.46</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51844,16 @@
           <t>327393901.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>299240731.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>299240731.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>357014905.9</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>973203895.34</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>973203895.34</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51870,10 @@
           <t>-126703838.9815971</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>327393901</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>327393901.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52039,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52223,11 @@
           <t>50.87</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>54.24</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>54.6</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>54.6</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52274,16 @@
           <t>375144116.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>320679037.4</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>320679037.4</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>363060922.7</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>1001978395.0</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>1001978395</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52300,10 @@
           <t>-134792169.8694002</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>375144116</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>375144116.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52469,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52653,11 @@
           <t>51.3</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>54.44</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>54.77</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>54.77</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52704,16 @@
           <t>338878390.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>303331772.4</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>303331772.4</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>376870119.1</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>1032089295.34</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>1032089295.34</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52730,10 @@
           <t>-146649016.6780689</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>338878390</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>338878390.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53083,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>54.42</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>54.92</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>54.92</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53134,16 @@
           <t>223387148.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>295501281.2</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>295501281.2</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>558935176.5</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>1080794822.2</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>1080794822.2</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53160,10 @@
           <t>-154464290.8805219</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>223387148</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>223387148.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53329,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53513,11 @@
           <t>94.96</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>96.38</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>98.56</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>98.56</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53564,16 @@
           <t>1707692568.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>590832121.2</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>590832121.2</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>543368572.0</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>872254029.78</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>872254029.78</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53590,10 @@
           <t>-1335174.697804213</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>1707692568</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>1707692568.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53759,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53943,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>96.54</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>98.36</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>98.36</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53994,16 @@
           <t>553548861.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>289179188.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>289179188.4</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>490488325.9</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>863763919.72</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>863763919.72</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54020,10 @@
           <t>-110970183.4100191</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>553548861</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>553548861.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54189,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54373,11 @@
           <t>89.67999999999999</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>96.66</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>98.36</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>98.36</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54424,16 @@
           <t>160084978.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>261713838.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>261713838.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>486209441.0</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>876442735.94</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>876442735.9400001</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54450,10 @@
           <t>-139970149.2699683</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>160084978</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>160084978.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54619,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54803,11 @@
           <t>90.3</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>97.65</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>98.49</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>98.48999999999999</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54854,16 @@
           <t>258569218.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>320629771.0</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>320629771</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>507572034.9</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>895038495.74</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>895038495.74</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54880,10 @@
           <t>-134242893.4173968</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>258569218</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>258569218.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55049,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55233,11 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>98.15</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>98.65</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>98.65000000000001</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55284,16 @@
           <t>274264981.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>378036382.6</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>378036382.6</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>519310939.4</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>907977233.66</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>907977233.66</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55310,10 @@
           <t>-131818593.1488162</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>274264981</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>274264981.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55479,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55663,11 @@
           <t>93.16</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>98.54</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>98.81</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>98.81</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55714,16 @@
           <t>199427904.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>495905022.8</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>495905022.8</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>546431748.5</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>920279550.14</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>920279550.14</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55740,10 @@
           <t>-125329189.045529</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>199427904</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>199427904.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55909,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56093,11 @@
           <t>95.48</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>99.17</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>98.99</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>98.98999999999999</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56144,16 @@
           <t>416222113.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>691797463.4</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>691797463.4</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>647418251.1</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>949116849.0</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>949116849</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56170,10 @@
           <t>-103564311.039207</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>416222113</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>416222113.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56339,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56523,11 @@
           <t>97.18</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>99.6</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>99.29</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>99.29000000000001</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56574,16 @@
           <t>454664639.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>710705043.2</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>710705043.2</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>672681304.1</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>964806938.22</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>964806938.22</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56600,10 @@
           <t>-92000853.74306107</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>454664639</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>454664639.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56769,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56953,11 @@
           <t>98.17999999999999</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>99.74</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>99.53</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>99.53</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57004,16 @@
           <t>545602276.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>694514298.8</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>694514298.8</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>685316274.5</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>1007368819.5</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>1007368819.5</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57030,10 @@
           <t>-76314726.32917178</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>545602276</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>545602276.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57199,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57383,11 @@
           <t>98.06</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>99.74</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>99.73999999999999</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57434,16 @@
           <t>863608182.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>660585496.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>660585496.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>751090903.6</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>1043269529.2</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>1043269529.2</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57460,10 @@
           <t>-60923765.19043088</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>863608182</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>863608182.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57629,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57813,11 @@
           <t>97.3</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>99.78</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>100.02</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>100.02</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57864,16 @@
           <t>1178890107.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>596958474.2</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>596958474.2</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>854175384.6</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>1109281994.18</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>1109281994.18</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57890,10 @@
           <t>-70832890.4497143</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>1178890107</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>1178890107.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58059,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58243,11 @@
           <t>78.91999999999999</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>82.38</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>81.54</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>81.54000000000001</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58294,16 @@
           <t>756633088.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>522324711.6</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>522324711.6</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>702009776.4</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>2096233546.2</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>2096233546.2</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58320,10 @@
           <t>-271965466.6952471</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>756633088</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>756633088.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58489,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58673,11 @@
           <t>77.94</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>82.6</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>81.43</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>81.43000000000001</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58724,16 @@
           <t>430099923.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>514860173.6</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>514860173.6</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>765340584.4</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>2126275527.62</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>2126275527.62</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58750,10 @@
           <t>-311632540.8864257</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>430099923</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>430099923.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58919,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59103,11 @@
           <t>77.67999999999999</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>82.93</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>81.38</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>81.38</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59154,16 @@
           <t>331696969.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>633904695.6</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>633904695.6</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>844095710.8</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>2165661771.46</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>2165661771.46</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59180,10 @@
           <t>-322184359.8778801</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>331696969</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>331696969.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59349,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59533,11 @@
           <t>78.47999999999999</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>81.4</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>81.40000000000001</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59584,16 @@
           <t>491858033.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>688076490.6</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>688076490.6</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>956654326.8</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>2224785548.32</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>2224785548.32</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59610,10 @@
           <t>-315208629.084319</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>491858033</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>491858033.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59779,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59963,11 @@
           <t>79.58000000000001</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>84.12</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>81.38</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>81.38</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60014,16 @@
           <t>601335545.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>800015008.4</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>800015008.4</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>1362004547.0</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>2241556713.92</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>2241556713.92</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60040,10 @@
           <t>-311145962.3405062</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>601335545</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>601335545.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60209,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60393,11 @@
           <t>80.72</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>84.64</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>81.3</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60444,16 @@
           <t>719310398.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>881694841.2</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>881694841.2</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>1450389791.4</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>2257409889.46</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>2257409889.46</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60470,10 @@
           <t>-305959530.337184</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>719310398</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>719310398.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60639,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60823,11 @@
           <t>82.04</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>85.21</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>81.26</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>81.26000000000001</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60874,16 @@
           <t>1025322533.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>1015820995.2</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>1015820995.2</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>1538938058.7</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>2289803775.58</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>2289803775.58</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60900,10 @@
           <t>-300263378.4989672</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>1025322533</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>1025322533.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61069,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61253,11 @@
           <t>83.34</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>85.64</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>81.22</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>81.22</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61304,16 @@
           <t>602555944.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>1054286726.0</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>1054286726</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>1543676929.3</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>2318867649.6</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>2318867649.6</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61330,10 @@
           <t>-314189341.105123</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>602555944</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>602555944.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61499,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61683,11 @@
           <t>83.84</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>85.88</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>81.09</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>81.09</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61734,16 @@
           <t>1051550622.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>1225232163.0</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>1225232163</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>1572435799.3</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>2346946243.34</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>2346946243.34</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61760,10 @@
           <t>-277566105.2530198</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>1051550622</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>1051550622.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61929,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62113,11 @@
           <t>84.0</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>86.23</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>80.97</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>80.97</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62164,16 @@
           <t>1009734709.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>1923994085.6</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>1923994085.6</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>1641851602.4</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>2405867904.04</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>2405867904.04</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62190,10 @@
           <t>-263440694.3481219</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>1009734709</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>1009734709.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
@@ -63221,7 +62359,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -63405,15 +62543,11 @@
           <t>83.60000000000001</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>86.27</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>80.88</t>
-        </is>
+      <c r="AM145" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>80.88</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -63460,20 +62594,16 @@
           <t>1389941168.0</t>
         </is>
       </c>
-      <c r="AX145" t="inlineStr">
-        <is>
-          <t>2019084741.6</t>
-        </is>
+      <c r="AX145" t="n">
+        <v>2019084741.6</v>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
           <t>1639501388.4</t>
         </is>
       </c>
-      <c r="AZ145" t="inlineStr">
-        <is>
-          <t>2455054011.18</t>
-        </is>
+      <c r="AZ145" t="n">
+        <v>2455054011.18</v>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
@@ -63490,8 +62620,10 @@
           <t>-229372663.2929773</t>
         </is>
       </c>
-      <c r="BD145" t="n">
-        <v>1389941168</v>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>1389941168.0</t>
+        </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
